--- a/구업가상육성기.xlsx
+++ b/구업가상육성기.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28fc1fc4d0c3d076/바탕 화면/가상육성기/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1286" documentId="8_{BB001725-052E-471A-AEAF-4EFB4A4064C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2291238-1497-4F6E-95E7-0D346120C69E}"/>
+  <xr:revisionPtr revIDLastSave="1400" documentId="8_{BB001725-052E-471A-AEAF-4EFB4A4064C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EADD5D15-50B9-4438-8B87-E1752CF5B9CC}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4350" yWindow="4785" windowWidth="14220" windowHeight="12720" xr2:uid="{87B9FB09-C1DD-422B-8452-C604D74272F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{87B9FB09-C1DD-422B-8452-C604D74272F1}"/>
   </bookViews>
   <sheets>
     <sheet name="스탯계산기" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="258">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -887,13 +887,1195 @@
   </si>
   <si>
     <t>와일드씽</t>
+  </si>
+  <si>
+    <t>등급</t>
+  </si>
+  <si>
+    <t>희귀도</t>
+  </si>
+  <si>
+    <t>1 돌파</t>
+  </si>
+  <si>
+    <t>2 돌파</t>
+  </si>
+  <si>
+    <t>3 돌파</t>
+  </si>
+  <si>
+    <t>4 돌파</t>
+  </si>
+  <si>
+    <t>5 돌파</t>
+  </si>
+  <si>
+    <t>6 돌파</t>
+  </si>
+  <si>
+    <t>총 파워 상승</t>
+  </si>
+  <si>
+    <t>5성</t>
+  </si>
+  <si>
+    <t>ROY / TEA / MMVP</t>
+  </si>
+  <si>
+    <t>POS / ASG/ SEA</t>
+  </si>
+  <si>
+    <t>1성</t>
+  </si>
+  <si>
+    <t>​</t>
+  </si>
+  <si>
+    <t>2성</t>
+  </si>
+  <si>
+    <t>3성</t>
+  </si>
+  <si>
+    <t>4성</t>
+  </si>
+  <si>
+    <t>TOP / ACE/ HIT / GG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>GRADE_CONSTANTS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"SEA"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"AGS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>},</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"POS"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ROY"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>},</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"MMVP"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"TEA"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>},</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"GG"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"ACE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>},</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"HIT"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">}, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"TOP"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>},</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DGN"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"atlas"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA5D6FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"enhance"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFBBBEBF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>SEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>희귀도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMVP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6돌파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급_희귀도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -949,8 +2131,57 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Inherit"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFBBBEBF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF79C0FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFA5D6FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -967,8 +2198,20 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E2E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -985,6 +2228,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD2D2D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFD2D2D2"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFD2D2D2"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD2D2D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFD2D2D2"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD2D2D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFD2D2D2"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD2D2D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD2D2D2"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD2D2D2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD2D2D2"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD2D2D2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFD2D2D2"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFD2D2D2"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD2D2D2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -997,7 +2342,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1020,6 +2365,51 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1359,13 +2749,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06CB73F4-EC94-4102-A612-6C04F01BA6F3}">
   <dimension ref="A1:P45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>161</v>
       </c>
@@ -1379,7 +2769,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="B2">
         <v>100</v>
       </c>
@@ -1391,7 +2781,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="B3" t="s">
         <v>212</v>
       </c>
@@ -1403,7 +2793,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="B4" t="s">
         <v>44</v>
       </c>
@@ -1411,7 +2801,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="B5" t="s">
         <v>55</v>
       </c>
@@ -1419,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -1427,7 +2817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="B7" t="s">
         <v>57</v>
       </c>
@@ -1435,7 +2825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="B8" t="s">
         <v>58</v>
       </c>
@@ -1443,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="C9" t="s">
         <v>59</v>
       </c>
@@ -1452,7 +2842,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -1484,7 +2874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>190</v>
       </c>
@@ -1504,7 +2894,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="C13" t="s">
         <v>31</v>
       </c>
@@ -1527,7 +2917,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13">
       <c r="C14" s="6" t="s">
         <v>188</v>
       </c>
@@ -1538,7 +2928,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13">
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
@@ -1580,7 +2970,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13">
       <c r="B16" s="3">
         <f>SUM(C16:J16)</f>
         <v>1899</v>
@@ -1611,7 +3001,7 @@
       </c>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="B17" t="s">
         <v>154</v>
       </c>
@@ -1628,7 +3018,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="B18" t="s">
         <v>155</v>
       </c>
@@ -1647,7 +3037,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
         <v>163</v>
       </c>
@@ -1679,27 +3069,27 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16">
       <c r="B24" t="s">
         <v>25</v>
       </c>
@@ -1722,7 +3112,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16">
       <c r="B25" t="s">
         <v>26</v>
       </c>
@@ -1748,7 +3138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16">
       <c r="B26" t="s">
         <v>27</v>
       </c>
@@ -1773,12 +3163,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16">
       <c r="B27" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16">
       <c r="B28" t="s">
         <v>31</v>
       </c>
@@ -1846,7 +3236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16">
       <c r="B29" t="s">
         <v>32</v>
       </c>
@@ -1914,7 +3304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16">
       <c r="B30" t="s">
         <v>33</v>
       </c>
@@ -1982,13 +3372,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16">
       <c r="P31">
         <f>32*28</f>
         <v>896</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -2017,7 +3407,7 @@
         <v>707.8</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -2046,7 +3436,7 @@
         <v>202.26400000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -2075,7 +3465,7 @@
         <v>134.4</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -2104,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -2133,7 +3523,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -2162,7 +3552,7 @@
         <v>179.2</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>156</v>
       </c>
@@ -2191,7 +3581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -2220,7 +3610,7 @@
         <v>1642.2639999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -2249,7 +3639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2278,7 +3668,7 @@
         <v>328.45280000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2307,7 +3697,7 @@
         <v>164.22640000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -2340,7 +3730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2369,7 +3759,7 @@
         <v>113.2</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>35</v>
       </c>
@@ -2459,7 +3849,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9BAF98-9596-48AE-99F7-06B3BCDAFA07}">
   <dimension ref="A1:L151"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.875" bestFit="1" customWidth="1"/>
@@ -2468,7 +3858,7 @@
     <col min="6" max="6" width="24.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="H1" t="s">
         <v>24</v>
       </c>
@@ -2479,7 +3869,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="17.25" thickBot="1">
       <c r="H2" s="4">
         <v>1</v>
       </c>
@@ -2496,7 +3886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="17.25" thickBot="1">
       <c r="H3" s="5">
         <v>2</v>
       </c>
@@ -2513,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="17.25" thickBot="1">
       <c r="H4" s="5">
         <v>3</v>
       </c>
@@ -2530,7 +3920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="17.25" thickBot="1">
       <c r="A5" t="s">
         <v>181</v>
       </c>
@@ -2565,7 +3955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="17.25" thickBot="1">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2603,7 +3993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="17.25" thickBot="1">
       <c r="H7" s="5">
         <v>6</v>
       </c>
@@ -2620,7 +4010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="17.25" thickBot="1">
       <c r="H8" s="5">
         <v>7</v>
       </c>
@@ -2637,7 +4027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="17.25" thickBot="1">
       <c r="H9" s="5">
         <v>8</v>
       </c>
@@ -2654,7 +4044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="17.25" thickBot="1">
       <c r="H10" s="5">
         <v>9</v>
       </c>
@@ -2671,7 +4061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="17.25" thickBot="1">
       <c r="H11" s="5">
         <v>10</v>
       </c>
@@ -2688,7 +4078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="17.25" thickBot="1">
       <c r="H12" s="5">
         <v>11</v>
       </c>
@@ -2705,7 +4095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="17.25" thickBot="1">
       <c r="H13" s="5">
         <v>12</v>
       </c>
@@ -2722,7 +4112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="17.25" thickBot="1">
       <c r="H14" s="5">
         <v>13</v>
       </c>
@@ -2739,7 +4129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="17.25" thickBot="1">
       <c r="H15" s="5">
         <v>14</v>
       </c>
@@ -2756,7 +4146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="17.25" thickBot="1">
       <c r="H16" s="5">
         <v>15</v>
       </c>
@@ -2773,7 +4163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="8:12" ht="17.25" thickBot="1">
       <c r="H17" s="5">
         <v>16</v>
       </c>
@@ -2790,7 +4180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="8:12" ht="17.25" thickBot="1">
       <c r="H18" s="5">
         <v>17</v>
       </c>
@@ -2807,7 +4197,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="8:12" ht="17.25" thickBot="1">
       <c r="H19" s="5">
         <v>18</v>
       </c>
@@ -2824,7 +4214,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="8:12" ht="17.25" thickBot="1">
       <c r="H20" s="5">
         <v>19</v>
       </c>
@@ -2841,7 +4231,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="8:12" ht="17.25" thickBot="1">
       <c r="H21" s="5">
         <v>20</v>
       </c>
@@ -2858,7 +4248,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="8:12" ht="17.25" thickBot="1">
       <c r="H22" s="5">
         <v>21</v>
       </c>
@@ -2875,7 +4265,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="8:12" ht="17.25" thickBot="1">
       <c r="H23" s="5">
         <v>22</v>
       </c>
@@ -2892,7 +4282,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="8:12" ht="17.25" thickBot="1">
       <c r="H24" s="5">
         <v>23</v>
       </c>
@@ -2909,7 +4299,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="8:12" ht="17.25" thickBot="1">
       <c r="H25" s="5">
         <v>24</v>
       </c>
@@ -2926,7 +4316,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="8:12" ht="17.25" thickBot="1">
       <c r="H26" s="5">
         <v>25</v>
       </c>
@@ -2943,7 +4333,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="8:12" ht="17.25" thickBot="1">
       <c r="H27" s="5">
         <v>26</v>
       </c>
@@ -2960,7 +4350,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="8:12" ht="17.25" thickBot="1">
       <c r="H28" s="5">
         <v>27</v>
       </c>
@@ -2977,7 +4367,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="8:12" ht="17.25" thickBot="1">
       <c r="H29" s="5">
         <v>28</v>
       </c>
@@ -2994,7 +4384,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="8:12" ht="17.25" thickBot="1">
       <c r="H30" s="5">
         <v>29</v>
       </c>
@@ -3011,7 +4401,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="8:12" ht="17.25" thickBot="1">
       <c r="H31" s="5">
         <v>30</v>
       </c>
@@ -3028,7 +4418,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="8:12" ht="17.25" thickBot="1">
       <c r="H32" s="5">
         <v>31</v>
       </c>
@@ -3045,7 +4435,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="8:12" ht="17.25" thickBot="1">
       <c r="H33" s="5">
         <v>32</v>
       </c>
@@ -3062,7 +4452,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="8:12" ht="17.25" thickBot="1">
       <c r="H34" s="5">
         <v>33</v>
       </c>
@@ -3079,7 +4469,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="35" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="8:12" ht="17.25" thickBot="1">
       <c r="H35" s="5">
         <v>34</v>
       </c>
@@ -3096,7 +4486,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="8:12" ht="17.25" thickBot="1">
       <c r="H36" s="5">
         <v>35</v>
       </c>
@@ -3113,7 +4503,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="37" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="8:12" ht="17.25" thickBot="1">
       <c r="H37" s="5">
         <v>36</v>
       </c>
@@ -3130,7 +4520,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="38" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="8:12" ht="17.25" thickBot="1">
       <c r="H38" s="5">
         <v>37</v>
       </c>
@@ -3147,7 +4537,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="39" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="8:12" ht="17.25" thickBot="1">
       <c r="H39" s="5">
         <v>38</v>
       </c>
@@ -3164,7 +4554,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="8:12" ht="17.25" thickBot="1">
       <c r="H40" s="5">
         <v>39</v>
       </c>
@@ -3181,7 +4571,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="8:12" ht="17.25" thickBot="1">
       <c r="H41" s="5">
         <v>40</v>
       </c>
@@ -3198,7 +4588,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="42" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="8:12" ht="17.25" thickBot="1">
       <c r="H42" s="5">
         <v>41</v>
       </c>
@@ -3215,7 +4605,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="43" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="8:12" ht="17.25" thickBot="1">
       <c r="H43" s="5">
         <v>42</v>
       </c>
@@ -3232,7 +4622,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="44" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="8:12" ht="17.25" thickBot="1">
       <c r="H44" s="5">
         <v>43</v>
       </c>
@@ -3249,7 +4639,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="45" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="8:12" ht="17.25" thickBot="1">
       <c r="H45" s="5">
         <v>44</v>
       </c>
@@ -3266,7 +4656,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="46" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="8:12" ht="17.25" thickBot="1">
       <c r="H46" s="5">
         <v>45</v>
       </c>
@@ -3283,7 +4673,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="47" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="8:12" ht="17.25" thickBot="1">
       <c r="H47" s="5">
         <v>46</v>
       </c>
@@ -3300,7 +4690,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="48" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="8:12" ht="17.25" thickBot="1">
       <c r="H48" s="5">
         <v>47</v>
       </c>
@@ -3317,7 +4707,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="49" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="8:12" ht="17.25" thickBot="1">
       <c r="H49" s="5">
         <v>48</v>
       </c>
@@ -3334,7 +4724,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="50" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="8:12" ht="17.25" thickBot="1">
       <c r="H50" s="5">
         <v>49</v>
       </c>
@@ -3351,7 +4741,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="51" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="8:12" ht="17.25" thickBot="1">
       <c r="H51" s="5">
         <v>50</v>
       </c>
@@ -3368,7 +4758,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="52" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="8:12" ht="17.25" thickBot="1">
       <c r="H52" s="5">
         <v>51</v>
       </c>
@@ -3385,7 +4775,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="53" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="8:12" ht="17.25" thickBot="1">
       <c r="H53" s="5">
         <v>52</v>
       </c>
@@ -3402,7 +4792,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="54" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="8:12" ht="17.25" thickBot="1">
       <c r="H54" s="5">
         <v>53</v>
       </c>
@@ -3419,7 +4809,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="55" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="8:12" ht="17.25" thickBot="1">
       <c r="H55" s="5">
         <v>54</v>
       </c>
@@ -3436,7 +4826,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="56" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="8:12" ht="17.25" thickBot="1">
       <c r="H56" s="5">
         <v>55</v>
       </c>
@@ -3453,7 +4843,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="57" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="8:12" ht="17.25" thickBot="1">
       <c r="H57" s="5">
         <v>56</v>
       </c>
@@ -3470,7 +4860,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="58" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="8:12" ht="17.25" thickBot="1">
       <c r="H58" s="5">
         <v>57</v>
       </c>
@@ -3487,7 +4877,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="59" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="8:12" ht="17.25" thickBot="1">
       <c r="H59" s="5">
         <v>58</v>
       </c>
@@ -3504,7 +4894,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="60" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="8:12" ht="17.25" thickBot="1">
       <c r="H60" s="5">
         <v>59</v>
       </c>
@@ -3521,7 +4911,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="61" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="8:12" ht="17.25" thickBot="1">
       <c r="H61" s="5">
         <v>60</v>
       </c>
@@ -3538,7 +4928,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="62" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="8:12" ht="17.25" thickBot="1">
       <c r="H62" s="5">
         <v>61</v>
       </c>
@@ -3555,7 +4945,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="63" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="8:12" ht="17.25" thickBot="1">
       <c r="H63" s="5">
         <v>62</v>
       </c>
@@ -3572,7 +4962,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="64" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="8:12" ht="17.25" thickBot="1">
       <c r="H64" s="5">
         <v>63</v>
       </c>
@@ -3589,7 +4979,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="65" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="8:12" ht="17.25" thickBot="1">
       <c r="H65" s="5">
         <v>64</v>
       </c>
@@ -3606,7 +4996,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="66" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="8:12" ht="17.25" thickBot="1">
       <c r="H66" s="5">
         <v>65</v>
       </c>
@@ -3623,7 +5013,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="67" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="8:12" ht="17.25" thickBot="1">
       <c r="H67" s="5">
         <v>66</v>
       </c>
@@ -3640,7 +5030,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="68" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="8:12" ht="17.25" thickBot="1">
       <c r="H68" s="5">
         <v>67</v>
       </c>
@@ -3657,7 +5047,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="69" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="8:12" ht="17.25" thickBot="1">
       <c r="H69" s="5">
         <v>68</v>
       </c>
@@ -3674,7 +5064,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="70" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="8:12" ht="17.25" thickBot="1">
       <c r="H70" s="5">
         <v>69</v>
       </c>
@@ -3691,7 +5081,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="71" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="8:12" ht="17.25" thickBot="1">
       <c r="H71" s="5">
         <v>70</v>
       </c>
@@ -3708,7 +5098,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="72" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="8:12" ht="17.25" thickBot="1">
       <c r="H72" s="5">
         <v>71</v>
       </c>
@@ -3725,7 +5115,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="73" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="8:12" ht="17.25" thickBot="1">
       <c r="H73" s="5">
         <v>72</v>
       </c>
@@ -3742,7 +5132,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="74" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="8:12" ht="17.25" thickBot="1">
       <c r="H74" s="5">
         <v>73</v>
       </c>
@@ -3759,7 +5149,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="75" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="8:12" ht="17.25" thickBot="1">
       <c r="H75" s="5">
         <v>74</v>
       </c>
@@ -3776,7 +5166,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="76" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="8:12" ht="17.25" thickBot="1">
       <c r="H76" s="5">
         <v>75</v>
       </c>
@@ -3793,7 +5183,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="77" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="8:12" ht="17.25" thickBot="1">
       <c r="H77" s="5">
         <v>76</v>
       </c>
@@ -3810,7 +5200,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="78" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="8:12" ht="17.25" thickBot="1">
       <c r="H78" s="5">
         <v>77</v>
       </c>
@@ -3827,7 +5217,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="79" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="8:12" ht="17.25" thickBot="1">
       <c r="H79" s="5">
         <v>78</v>
       </c>
@@ -3844,7 +5234,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="80" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="8:12" ht="17.25" thickBot="1">
       <c r="H80" s="5">
         <v>79</v>
       </c>
@@ -3861,7 +5251,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="81" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="8:12" ht="17.25" thickBot="1">
       <c r="H81" s="5">
         <v>80</v>
       </c>
@@ -3878,7 +5268,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="82" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="8:12" ht="17.25" thickBot="1">
       <c r="H82" s="5">
         <v>81</v>
       </c>
@@ -3895,7 +5285,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="83" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="8:12" ht="17.25" thickBot="1">
       <c r="H83" s="5">
         <v>82</v>
       </c>
@@ -3912,7 +5302,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="84" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="8:12" ht="17.25" thickBot="1">
       <c r="H84" s="5">
         <v>83</v>
       </c>
@@ -3929,7 +5319,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="85" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="8:12" ht="17.25" thickBot="1">
       <c r="H85" s="5">
         <v>84</v>
       </c>
@@ -3946,7 +5336,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="86" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="8:12" ht="17.25" thickBot="1">
       <c r="H86" s="5">
         <v>85</v>
       </c>
@@ -3963,7 +5353,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="87" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="8:12" ht="17.25" thickBot="1">
       <c r="H87" s="5">
         <v>86</v>
       </c>
@@ -3980,7 +5370,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="88" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="8:12" ht="17.25" thickBot="1">
       <c r="H88" s="5">
         <v>87</v>
       </c>
@@ -3997,7 +5387,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="89" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="8:12" ht="17.25" thickBot="1">
       <c r="H89" s="5">
         <v>88</v>
       </c>
@@ -4014,7 +5404,7 @@
         <v>2588</v>
       </c>
     </row>
-    <row r="90" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="8:12" ht="17.25" thickBot="1">
       <c r="H90" s="5">
         <v>89</v>
       </c>
@@ -4031,7 +5421,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="91" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="8:12" ht="17.25" thickBot="1">
       <c r="H91" s="5">
         <v>90</v>
       </c>
@@ -4048,7 +5438,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="92" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="8:12" ht="17.25" thickBot="1">
       <c r="H92" s="5">
         <v>91</v>
       </c>
@@ -4065,7 +5455,7 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="93" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="8:12" ht="17.25" thickBot="1">
       <c r="H93" s="5">
         <v>92</v>
       </c>
@@ -4082,7 +5472,7 @@
         <v>2898</v>
       </c>
     </row>
-    <row r="94" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="8:12" ht="17.25" thickBot="1">
       <c r="H94" s="5">
         <v>93</v>
       </c>
@@ -4099,7 +5489,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="95" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="8:12" ht="17.25" thickBot="1">
       <c r="H95" s="5">
         <v>94</v>
       </c>
@@ -4116,7 +5506,7 @@
         <v>3058</v>
       </c>
     </row>
-    <row r="96" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="8:12" ht="17.25" thickBot="1">
       <c r="H96" s="5">
         <v>95</v>
       </c>
@@ -4133,7 +5523,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="97" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="8:12" ht="17.25" thickBot="1">
       <c r="H97" s="5">
         <v>96</v>
       </c>
@@ -4150,7 +5540,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="98" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="8:12" ht="17.25" thickBot="1">
       <c r="H98" s="5">
         <v>97</v>
       </c>
@@ -4167,7 +5557,7 @@
         <v>3328</v>
       </c>
     </row>
-    <row r="99" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="8:12" ht="17.25" thickBot="1">
       <c r="H99" s="5">
         <v>98</v>
       </c>
@@ -4184,7 +5574,7 @@
         <v>3418</v>
       </c>
     </row>
-    <row r="100" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="8:12" ht="17.25" thickBot="1">
       <c r="H100" s="5">
         <v>99</v>
       </c>
@@ -4201,7 +5591,7 @@
         <v>3508</v>
       </c>
     </row>
-    <row r="101" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="8:12" ht="17.25" thickBot="1">
       <c r="H101" s="5">
         <v>100</v>
       </c>
@@ -4218,7 +5608,7 @@
         <v>3608</v>
       </c>
     </row>
-    <row r="102" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="8:12" ht="17.25" thickBot="1">
       <c r="H102" s="5">
         <v>101</v>
       </c>
@@ -4235,7 +5625,7 @@
         <v>3708</v>
       </c>
     </row>
-    <row r="103" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="8:12" ht="17.25" thickBot="1">
       <c r="H103" s="5">
         <v>102</v>
       </c>
@@ -4252,7 +5642,7 @@
         <v>3808</v>
       </c>
     </row>
-    <row r="104" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="8:12" ht="17.25" thickBot="1">
       <c r="H104" s="5">
         <v>103</v>
       </c>
@@ -4269,7 +5659,7 @@
         <v>3908</v>
       </c>
     </row>
-    <row r="105" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="8:12" ht="17.25" thickBot="1">
       <c r="H105" s="5">
         <v>104</v>
       </c>
@@ -4286,7 +5676,7 @@
         <v>4008</v>
       </c>
     </row>
-    <row r="106" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="8:12" ht="17.25" thickBot="1">
       <c r="H106" s="5">
         <v>105</v>
       </c>
@@ -4303,7 +5693,7 @@
         <v>4108</v>
       </c>
     </row>
-    <row r="107" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="8:12" ht="17.25" thickBot="1">
       <c r="H107" s="5">
         <v>106</v>
       </c>
@@ -4320,7 +5710,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="108" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="8:12" ht="17.25" thickBot="1">
       <c r="H108" s="5">
         <v>107</v>
       </c>
@@ -4337,7 +5727,7 @@
         <v>4308</v>
       </c>
     </row>
-    <row r="109" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="8:12" ht="17.25" thickBot="1">
       <c r="H109" s="5">
         <v>108</v>
       </c>
@@ -4354,7 +5744,7 @@
         <v>4408</v>
       </c>
     </row>
-    <row r="110" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="8:12" ht="17.25" thickBot="1">
       <c r="H110" s="5">
         <v>109</v>
       </c>
@@ -4371,7 +5761,7 @@
         <v>4508</v>
       </c>
     </row>
-    <row r="111" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="8:12" ht="17.25" thickBot="1">
       <c r="H111" s="5">
         <v>110</v>
       </c>
@@ -4388,7 +5778,7 @@
         <v>4608</v>
       </c>
     </row>
-    <row r="112" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="8:12" ht="17.25" thickBot="1">
       <c r="H112" s="5">
         <v>111</v>
       </c>
@@ -4405,7 +5795,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="113" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="8:12" ht="17.25" thickBot="1">
       <c r="H113" s="5">
         <v>112</v>
       </c>
@@ -4422,7 +5812,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="114" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="8:12" ht="17.25" thickBot="1">
       <c r="H114" s="5">
         <v>113</v>
       </c>
@@ -4439,7 +5829,7 @@
         <v>4908</v>
       </c>
     </row>
-    <row r="115" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="8:12" ht="17.25" thickBot="1">
       <c r="H115" s="5">
         <v>114</v>
       </c>
@@ -4456,7 +5846,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="116" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="8:12" ht="17.25" thickBot="1">
       <c r="H116" s="5">
         <v>115</v>
       </c>
@@ -4473,7 +5863,7 @@
         <v>5108</v>
       </c>
     </row>
-    <row r="117" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="8:12" ht="17.25" thickBot="1">
       <c r="H117" s="5">
         <v>116</v>
       </c>
@@ -4490,7 +5880,7 @@
         <v>5208</v>
       </c>
     </row>
-    <row r="118" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="8:12" ht="17.25" thickBot="1">
       <c r="H118" s="5">
         <v>117</v>
       </c>
@@ -4507,7 +5897,7 @@
         <v>5308</v>
       </c>
     </row>
-    <row r="119" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="8:12" ht="17.25" thickBot="1">
       <c r="H119" s="5">
         <v>118</v>
       </c>
@@ -4524,7 +5914,7 @@
         <v>5408</v>
       </c>
     </row>
-    <row r="120" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="8:12" ht="17.25" thickBot="1">
       <c r="H120" s="5">
         <v>119</v>
       </c>
@@ -4541,7 +5931,7 @@
         <v>5508</v>
       </c>
     </row>
-    <row r="121" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="8:12" ht="17.25" thickBot="1">
       <c r="H121" s="5">
         <v>120</v>
       </c>
@@ -4558,7 +5948,7 @@
         <v>5608</v>
       </c>
     </row>
-    <row r="122" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="8:12" ht="17.25" thickBot="1">
       <c r="H122" s="5">
         <v>121</v>
       </c>
@@ -4575,7 +5965,7 @@
         <v>5708</v>
       </c>
     </row>
-    <row r="123" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="8:12" ht="17.25" thickBot="1">
       <c r="H123" s="5">
         <v>122</v>
       </c>
@@ -4592,7 +5982,7 @@
         <v>5808</v>
       </c>
     </row>
-    <row r="124" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="8:12" ht="17.25" thickBot="1">
       <c r="H124" s="5">
         <v>123</v>
       </c>
@@ -4609,7 +5999,7 @@
         <v>5908</v>
       </c>
     </row>
-    <row r="125" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="8:12" ht="17.25" thickBot="1">
       <c r="H125" s="5">
         <v>124</v>
       </c>
@@ -4626,7 +6016,7 @@
         <v>6008</v>
       </c>
     </row>
-    <row r="126" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="8:12" ht="17.25" thickBot="1">
       <c r="H126" s="5">
         <v>125</v>
       </c>
@@ -4643,7 +6033,7 @@
         <v>6108</v>
       </c>
     </row>
-    <row r="127" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="8:12" ht="17.25" thickBot="1">
       <c r="H127" s="5">
         <v>126</v>
       </c>
@@ -4660,7 +6050,7 @@
         <v>6208</v>
       </c>
     </row>
-    <row r="128" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="8:12" ht="17.25" thickBot="1">
       <c r="H128" s="5">
         <v>127</v>
       </c>
@@ -4677,7 +6067,7 @@
         <v>6308</v>
       </c>
     </row>
-    <row r="129" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="8:12" ht="17.25" thickBot="1">
       <c r="H129" s="5">
         <v>128</v>
       </c>
@@ -4694,7 +6084,7 @@
         <v>6408</v>
       </c>
     </row>
-    <row r="130" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="8:12" ht="17.25" thickBot="1">
       <c r="H130" s="5">
         <v>129</v>
       </c>
@@ -4711,7 +6101,7 @@
         <v>6508</v>
       </c>
     </row>
-    <row r="131" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="8:12" ht="17.25" thickBot="1">
       <c r="H131" s="5">
         <v>130</v>
       </c>
@@ -4728,7 +6118,7 @@
         <v>6608</v>
       </c>
     </row>
-    <row r="132" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="8:12" ht="17.25" thickBot="1">
       <c r="H132" s="5">
         <v>131</v>
       </c>
@@ -4745,7 +6135,7 @@
         <v>6708</v>
       </c>
     </row>
-    <row r="133" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="8:12" ht="17.25" thickBot="1">
       <c r="H133" s="5">
         <v>132</v>
       </c>
@@ -4762,7 +6152,7 @@
         <v>6808</v>
       </c>
     </row>
-    <row r="134" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="8:12" ht="17.25" thickBot="1">
       <c r="H134" s="5">
         <v>133</v>
       </c>
@@ -4779,7 +6169,7 @@
         <v>6908</v>
       </c>
     </row>
-    <row r="135" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="8:12" ht="17.25" thickBot="1">
       <c r="H135" s="5">
         <v>134</v>
       </c>
@@ -4796,7 +6186,7 @@
         <v>7008</v>
       </c>
     </row>
-    <row r="136" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="8:12" ht="17.25" thickBot="1">
       <c r="H136" s="5">
         <v>135</v>
       </c>
@@ -4813,7 +6203,7 @@
         <v>7108</v>
       </c>
     </row>
-    <row r="137" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="8:12" ht="17.25" thickBot="1">
       <c r="H137" s="5">
         <v>136</v>
       </c>
@@ -4830,7 +6220,7 @@
         <v>7208</v>
       </c>
     </row>
-    <row r="138" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="8:12" ht="17.25" thickBot="1">
       <c r="H138" s="5">
         <v>137</v>
       </c>
@@ -4847,7 +6237,7 @@
         <v>7308</v>
       </c>
     </row>
-    <row r="139" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="8:12" ht="17.25" thickBot="1">
       <c r="H139" s="5">
         <v>138</v>
       </c>
@@ -4864,7 +6254,7 @@
         <v>7408</v>
       </c>
     </row>
-    <row r="140" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="8:12" ht="17.25" thickBot="1">
       <c r="H140" s="5">
         <v>139</v>
       </c>
@@ -4881,7 +6271,7 @@
         <v>7508</v>
       </c>
     </row>
-    <row r="141" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="8:12" ht="17.25" thickBot="1">
       <c r="H141" s="5">
         <v>140</v>
       </c>
@@ -4898,7 +6288,7 @@
         <v>7608</v>
       </c>
     </row>
-    <row r="142" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="8:12" ht="17.25" thickBot="1">
       <c r="H142" s="5">
         <v>141</v>
       </c>
@@ -4915,7 +6305,7 @@
         <v>7708</v>
       </c>
     </row>
-    <row r="143" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="8:12" ht="17.25" thickBot="1">
       <c r="H143" s="5">
         <v>142</v>
       </c>
@@ -4932,7 +6322,7 @@
         <v>7808</v>
       </c>
     </row>
-    <row r="144" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="8:12" ht="17.25" thickBot="1">
       <c r="H144" s="5">
         <v>143</v>
       </c>
@@ -4949,7 +6339,7 @@
         <v>7908</v>
       </c>
     </row>
-    <row r="145" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="8:12" ht="17.25" thickBot="1">
       <c r="H145" s="5">
         <v>144</v>
       </c>
@@ -4966,7 +6356,7 @@
         <v>8008</v>
       </c>
     </row>
-    <row r="146" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="8:12" ht="17.25" thickBot="1">
       <c r="H146" s="5">
         <v>145</v>
       </c>
@@ -4983,7 +6373,7 @@
         <v>8108</v>
       </c>
     </row>
-    <row r="147" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="8:12" ht="17.25" thickBot="1">
       <c r="H147" s="5">
         <v>146</v>
       </c>
@@ -5000,7 +6390,7 @@
         <v>8208</v>
       </c>
     </row>
-    <row r="148" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="8:12" ht="17.25" thickBot="1">
       <c r="H148" s="5">
         <v>147</v>
       </c>
@@ -5017,7 +6407,7 @@
         <v>8308</v>
       </c>
     </row>
-    <row r="149" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="8:12" ht="17.25" thickBot="1">
       <c r="H149" s="5">
         <v>148</v>
       </c>
@@ -5034,7 +6424,7 @@
         <v>8408</v>
       </c>
     </row>
-    <row r="150" spans="8:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="8:12" ht="17.25" thickBot="1">
       <c r="H150" s="5">
         <v>149</v>
       </c>
@@ -5051,7 +6441,7 @@
         <v>8508</v>
       </c>
     </row>
-    <row r="151" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="8:12">
       <c r="H151" s="5">
         <v>150</v>
       </c>
@@ -5082,7 +6472,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0431008-3D8B-407C-9D1E-C91145F3C876}">
   <dimension ref="A1:U44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="7" max="7" width="5.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.25" bestFit="1" customWidth="1"/>
@@ -5095,7 +6485,7 @@
     <col min="17" max="20" width="5.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5160,7 +6550,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -5183,7 +6573,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -5197,7 +6587,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
         <v>117</v>
       </c>
@@ -5211,7 +6601,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -5231,7 +6621,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -5245,7 +6635,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -5262,7 +6652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -5279,7 +6669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -5305,7 +6695,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -5331,7 +6721,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -5348,7 +6738,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -5359,7 +6749,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -5370,7 +6760,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
         <v>127</v>
       </c>
@@ -5390,7 +6780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -5407,7 +6797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -5418,7 +6808,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -5438,7 +6828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20">
       <c r="A18" t="s">
         <v>131</v>
       </c>
@@ -5458,7 +6848,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -5478,7 +6868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20">
       <c r="A20" t="s">
         <v>133</v>
       </c>
@@ -5498,7 +6888,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
         <v>134</v>
       </c>
@@ -5509,7 +6899,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20">
       <c r="A22" t="s">
         <v>135</v>
       </c>
@@ -5520,7 +6910,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20">
       <c r="A23" t="s">
         <v>136</v>
       </c>
@@ -5528,7 +6918,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
         <v>137</v>
       </c>
@@ -5536,7 +6926,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20">
       <c r="A25" t="s">
         <v>138</v>
       </c>
@@ -5547,7 +6937,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20">
       <c r="A26" t="s">
         <v>139</v>
       </c>
@@ -5555,7 +6945,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20">
       <c r="A27" t="s">
         <v>140</v>
       </c>
@@ -5563,7 +6953,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20">
       <c r="A28" t="s">
         <v>141</v>
       </c>
@@ -5574,7 +6964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -5594,7 +6984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20">
       <c r="A30" t="s">
         <v>143</v>
       </c>
@@ -5605,7 +6995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20">
       <c r="A31" t="s">
         <v>144</v>
       </c>
@@ -5616,7 +7006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -5633,7 +7023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20">
       <c r="A33" t="s">
         <v>146</v>
       </c>
@@ -5644,7 +7034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20">
       <c r="A34" t="s">
         <v>147</v>
       </c>
@@ -5661,7 +7051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20">
       <c r="A35" t="s">
         <v>148</v>
       </c>
@@ -5672,7 +7062,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20">
       <c r="A36" t="s">
         <v>149</v>
       </c>
@@ -5683,7 +7073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20">
       <c r="K37" t="s">
         <v>100</v>
       </c>
@@ -5691,7 +7081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20">
       <c r="K38" t="s">
         <v>101</v>
       </c>
@@ -5699,7 +7089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20">
       <c r="K39" t="s">
         <v>102</v>
       </c>
@@ -5707,7 +7097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20">
       <c r="K40" t="s">
         <v>103</v>
       </c>
@@ -5715,7 +7105,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20">
       <c r="K41" t="s">
         <v>104</v>
       </c>
@@ -5723,17 +7113,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20">
       <c r="K42" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20">
       <c r="K43" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20">
       <c r="K44" t="s">
         <v>114</v>
       </c>
@@ -5746,13 +7136,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282C6102-A22E-4950-9997-45B6C37E4186}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T33"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -5766,7 +7156,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5780,7 +7170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -5794,7 +7184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5808,7 +7198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="17.25" thickBot="1">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5822,7 +7212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="27" thickTop="1" thickBot="1">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5835,8 +7225,35 @@
       <c r="G6">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L6" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="T6" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="39" thickBot="1">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -5849,8 +7266,35 @@
       <c r="G7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L7" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="N7" s="9">
+        <v>100</v>
+      </c>
+      <c r="O7" s="9">
+        <v>150</v>
+      </c>
+      <c r="P7" s="9">
+        <v>200</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>250</v>
+      </c>
+      <c r="R7" s="9">
+        <v>300</v>
+      </c>
+      <c r="S7" s="9">
+        <v>500</v>
+      </c>
+      <c r="T7" s="10">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="26.25" thickBot="1">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -5863,8 +7307,33 @@
       <c r="G8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L8" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="8">
+        <v>50</v>
+      </c>
+      <c r="O8" s="8">
+        <v>100</v>
+      </c>
+      <c r="P8" s="8">
+        <v>150</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>200</v>
+      </c>
+      <c r="R8" s="8">
+        <v>250</v>
+      </c>
+      <c r="S8" s="8">
+        <v>300</v>
+      </c>
+      <c r="T8" s="10">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="27" thickTop="1" thickBot="1">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -5877,8 +7346,35 @@
       <c r="G9">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L9" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="R9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="T9" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="17.25" thickBot="1">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5891,8 +7387,35 @@
       <c r="G10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L10" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="N10" s="8">
+        <v>30</v>
+      </c>
+      <c r="O10" s="8">
+        <v>60</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="T10" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="17.25" thickBot="1">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -5905,8 +7428,33 @@
       <c r="G11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L11" s="17"/>
+      <c r="M11" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="N11" s="8">
+        <v>30</v>
+      </c>
+      <c r="O11" s="8">
+        <v>60</v>
+      </c>
+      <c r="P11" s="8">
+        <v>90</v>
+      </c>
+      <c r="Q11" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="R11" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="S11" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="T11" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="17.25" thickBot="1">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -5919,33 +7467,537 @@
       <c r="G12">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L12" s="17"/>
+      <c r="M12" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="N12" s="8">
+        <v>30</v>
+      </c>
+      <c r="O12" s="8">
+        <v>60</v>
+      </c>
+      <c r="P12" s="8">
+        <v>90</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>120</v>
+      </c>
+      <c r="R12" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="S12" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="T12" s="9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="17.25" thickBot="1">
       <c r="G13">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L13" s="17"/>
+      <c r="M13" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="N13" s="8">
+        <v>30</v>
+      </c>
+      <c r="O13" s="8">
+        <v>60</v>
+      </c>
+      <c r="P13" s="8">
+        <v>90</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>120</v>
+      </c>
+      <c r="R13" s="8">
+        <v>150</v>
+      </c>
+      <c r="S13" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="T13" s="9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="17.25" thickBot="1">
       <c r="G14">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L14" s="19"/>
+      <c r="M14" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="N14" s="9">
+        <v>30</v>
+      </c>
+      <c r="O14" s="9">
+        <v>60</v>
+      </c>
+      <c r="P14" s="9">
+        <v>90</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>120</v>
+      </c>
+      <c r="R14" s="9">
+        <v>150</v>
+      </c>
+      <c r="S14" s="9">
+        <v>180</v>
+      </c>
+      <c r="T14" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="G15">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="L15" s="20" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="G16">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19">
       <c r="G17">
         <v>15</v>
       </c>
+      <c r="L17" t="s">
+        <v>257</v>
+      </c>
+      <c r="M17" t="s">
+        <v>242</v>
+      </c>
+      <c r="N17" t="s">
+        <v>251</v>
+      </c>
+      <c r="O17" t="s">
+        <v>252</v>
+      </c>
+      <c r="P17" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>254</v>
+      </c>
+      <c r="R17" t="s">
+        <v>255</v>
+      </c>
+      <c r="S17" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="L18" t="s">
+        <v>240</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>30</v>
+      </c>
+      <c r="O18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="L19" t="s">
+        <v>240</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>30</v>
+      </c>
+      <c r="O19">
+        <v>90</v>
+      </c>
+      <c r="P19">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="L20" t="s">
+        <v>240</v>
+      </c>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="N20">
+        <v>30</v>
+      </c>
+      <c r="O20">
+        <v>90</v>
+      </c>
+      <c r="P20">
+        <v>180</v>
+      </c>
+      <c r="Q20">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="L21" t="s">
+        <v>240</v>
+      </c>
+      <c r="M21">
+        <v>4</v>
+      </c>
+      <c r="N21">
+        <v>30</v>
+      </c>
+      <c r="O21">
+        <v>90</v>
+      </c>
+      <c r="P21">
+        <v>180</v>
+      </c>
+      <c r="Q21">
+        <v>300</v>
+      </c>
+      <c r="R21">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="L22" t="s">
+        <v>240</v>
+      </c>
+      <c r="M22">
+        <v>5</v>
+      </c>
+      <c r="N22">
+        <v>90</v>
+      </c>
+      <c r="O22">
+        <v>90</v>
+      </c>
+      <c r="P22">
+        <v>180</v>
+      </c>
+      <c r="Q22">
+        <v>300</v>
+      </c>
+      <c r="R22">
+        <v>450</v>
+      </c>
+      <c r="S22">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s">
+        <v>241</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>30</v>
+      </c>
+      <c r="O23">
+        <v>90</v>
+      </c>
+      <c r="P23">
+        <v>180</v>
+      </c>
+      <c r="Q23">
+        <v>300</v>
+      </c>
+      <c r="R23">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="L24" t="s">
+        <v>241</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
+      </c>
+      <c r="N24">
+        <v>90</v>
+      </c>
+      <c r="O24">
+        <v>90</v>
+      </c>
+      <c r="P24">
+        <v>180</v>
+      </c>
+      <c r="Q24">
+        <v>300</v>
+      </c>
+      <c r="R24">
+        <v>450</v>
+      </c>
+      <c r="S24">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s">
+        <v>243</v>
+      </c>
+      <c r="M25">
+        <v>3</v>
+      </c>
+      <c r="N25">
+        <v>30</v>
+      </c>
+      <c r="O25">
+        <v>90</v>
+      </c>
+      <c r="P25">
+        <v>180</v>
+      </c>
+      <c r="Q25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="L26" t="s">
+        <v>243</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>30</v>
+      </c>
+      <c r="O26">
+        <v>90</v>
+      </c>
+      <c r="P26">
+        <v>180</v>
+      </c>
+      <c r="Q26">
+        <v>300</v>
+      </c>
+      <c r="R26">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="L27" t="s">
+        <v>246</v>
+      </c>
+      <c r="M27">
+        <v>5</v>
+      </c>
+      <c r="N27">
+        <v>50</v>
+      </c>
+      <c r="O27">
+        <v>150</v>
+      </c>
+      <c r="P27">
+        <v>300</v>
+      </c>
+      <c r="Q27">
+        <v>500</v>
+      </c>
+      <c r="R27">
+        <v>750</v>
+      </c>
+      <c r="S27">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="L28" t="s">
+        <v>247</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
+      <c r="N28">
+        <v>50</v>
+      </c>
+      <c r="O28">
+        <v>150</v>
+      </c>
+      <c r="P28">
+        <v>300</v>
+      </c>
+      <c r="Q28">
+        <v>500</v>
+      </c>
+      <c r="R28">
+        <v>750</v>
+      </c>
+      <c r="S28">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="L29" t="s">
+        <v>248</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
+      </c>
+      <c r="N29">
+        <v>50</v>
+      </c>
+      <c r="O29">
+        <v>150</v>
+      </c>
+      <c r="P29">
+        <v>300</v>
+      </c>
+      <c r="Q29">
+        <v>500</v>
+      </c>
+      <c r="R29">
+        <v>750</v>
+      </c>
+      <c r="S29">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="L30" t="s">
+        <v>249</v>
+      </c>
+      <c r="M30">
+        <v>5</v>
+      </c>
+      <c r="N30">
+        <v>100</v>
+      </c>
+      <c r="O30">
+        <v>250</v>
+      </c>
+      <c r="P30">
+        <v>450</v>
+      </c>
+      <c r="Q30">
+        <v>700</v>
+      </c>
+      <c r="R30">
+        <v>1000</v>
+      </c>
+      <c r="S30">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="L31" t="s">
+        <v>245</v>
+      </c>
+      <c r="M31">
+        <v>5</v>
+      </c>
+      <c r="N31">
+        <v>100</v>
+      </c>
+      <c r="O31">
+        <v>250</v>
+      </c>
+      <c r="P31">
+        <v>450</v>
+      </c>
+      <c r="Q31">
+        <v>700</v>
+      </c>
+      <c r="R31">
+        <v>1000</v>
+      </c>
+      <c r="S31">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="L32" t="s">
+        <v>244</v>
+      </c>
+      <c r="M32">
+        <v>5</v>
+      </c>
+      <c r="N32">
+        <v>100</v>
+      </c>
+      <c r="O32">
+        <v>250</v>
+      </c>
+      <c r="P32">
+        <v>450</v>
+      </c>
+      <c r="Q32">
+        <v>700</v>
+      </c>
+      <c r="R32">
+        <v>1000</v>
+      </c>
+      <c r="S32">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33" spans="12:19">
+      <c r="L33" t="s">
+        <v>250</v>
+      </c>
+      <c r="M33">
+        <v>5</v>
+      </c>
+      <c r="N33">
+        <v>100</v>
+      </c>
+      <c r="O33">
+        <v>250</v>
+      </c>
+      <c r="P33">
+        <v>450</v>
+      </c>
+      <c r="Q33">
+        <v>700</v>
+      </c>
+      <c r="R33">
+        <v>1000</v>
+      </c>
+      <c r="S33">
+        <v>1500</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="L10:L14"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5954,9 +8006,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F656B936-F47C-42EC-B2FE-D7AB4B9ADA7A}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>198</v>
       </c>
@@ -5970,7 +8022,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -5981,7 +8033,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>200</v>
       </c>
@@ -5992,7 +8044,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>201</v>
       </c>
@@ -6000,7 +8052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>202</v>
       </c>
@@ -6008,7 +8060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>203</v>
       </c>
@@ -6016,7 +8068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>204</v>
       </c>
@@ -6024,7 +8076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>205</v>
       </c>
@@ -6032,7 +8084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>198</v>
       </c>
@@ -6040,7 +8092,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -6048,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>207</v>
       </c>
@@ -6056,7 +8108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>208</v>
       </c>
@@ -6064,7 +8116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -6072,7 +8124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -6080,7 +8132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>204</v>
       </c>
@@ -6088,7 +8140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>205</v>
       </c>
@@ -6096,12 +8148,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14">
       <c r="F27" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14">
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="str">
         <f>IF(F23="투수","무브먼트","컨택트")</f>
@@ -6135,7 +8187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14">
       <c r="F29" t="s">
         <v>154</v>
       </c>
@@ -6158,7 +8210,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14">
       <c r="F30" t="s">
         <v>155</v>
       </c>
@@ -6186,9 +8238,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7810271-E7B4-494B-B56A-FCC58CC9DE96}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>150</v>
       </c>
@@ -6196,7 +8248,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>151</v>
       </c>

--- a/구업가상육성기.xlsx
+++ b/구업가상육성기.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/28fc1fc4d0c3d076/바탕 화면/가상육성기/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1400" documentId="8_{BB001725-052E-471A-AEAF-4EFB4A4064C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EADD5D15-50B9-4438-8B87-E1752CF5B9CC}"/>
+  <xr:revisionPtr revIDLastSave="1403" documentId="8_{BB001725-052E-471A-AEAF-4EFB4A4064C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2265C33D-3690-43E8-8C0C-67EF4F19EFB3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{87B9FB09-C1DD-422B-8452-C604D74272F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{87B9FB09-C1DD-422B-8452-C604D74272F1}"/>
   </bookViews>
   <sheets>
     <sheet name="스탯계산기" sheetId="1" r:id="rId1"/>
@@ -2385,22 +2385,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2411,6 +2396,21 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3957,25 +3957,25 @@
     </row>
     <row r="6" spans="1:12" ht="17.25" thickBot="1">
       <c r="A6">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1588</v>
       </c>
       <c r="C6">
         <f>VLOOKUP(A6,H2:L151,3,FALSE) + B6</f>
-        <v>0</v>
+        <v>1691</v>
       </c>
       <c r="D6">
         <v>150</v>
       </c>
       <c r="E6">
         <f>IF(D6&gt;A6,VLOOKUP(D6,H2:L151,3,FALSE)-C6,0)</f>
-        <v>1693</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <f>_xlfn.XLOOKUP(C6, J2:J151, H2:H151, , -1)</f>
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="H6" s="5">
         <v>5</v>
@@ -7269,7 +7269,7 @@
       <c r="L7" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="18" t="s">
         <v>223</v>
       </c>
       <c r="N7" s="9">
@@ -7310,7 +7310,7 @@
       <c r="L8" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="M8" s="15"/>
+      <c r="M8" s="19"/>
       <c r="N8" s="8">
         <v>50</v>
       </c>
@@ -7387,7 +7387,7 @@
       <c r="G10">
         <v>8</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="20" t="s">
         <v>225</v>
       </c>
       <c r="M10" s="8" t="s">
@@ -7399,16 +7399,16 @@
       <c r="O10" s="8">
         <v>60</v>
       </c>
-      <c r="P10" s="16" t="s">
+      <c r="P10" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="Q10" s="16" t="s">
+      <c r="Q10" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="R10" s="16" t="s">
+      <c r="R10" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="S10" s="16" t="s">
+      <c r="S10" s="14" t="s">
         <v>227</v>
       </c>
       <c r="T10" s="9">
@@ -7428,7 +7428,7 @@
       <c r="G11">
         <v>9</v>
       </c>
-      <c r="L11" s="17"/>
+      <c r="L11" s="21"/>
       <c r="M11" s="8" t="s">
         <v>228</v>
       </c>
@@ -7441,13 +7441,13 @@
       <c r="P11" s="8">
         <v>90</v>
       </c>
-      <c r="Q11" s="16" t="s">
+      <c r="Q11" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="R11" s="16" t="s">
+      <c r="R11" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="S11" s="16" t="s">
+      <c r="S11" s="14" t="s">
         <v>227</v>
       </c>
       <c r="T11" s="9">
@@ -7467,7 +7467,7 @@
       <c r="G12">
         <v>10</v>
       </c>
-      <c r="L12" s="17"/>
+      <c r="L12" s="21"/>
       <c r="M12" s="8" t="s">
         <v>229</v>
       </c>
@@ -7483,10 +7483,10 @@
       <c r="Q12" s="8">
         <v>120</v>
       </c>
-      <c r="R12" s="16" t="s">
+      <c r="R12" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="S12" s="14" t="s">
         <v>227</v>
       </c>
       <c r="T12" s="9">
@@ -7497,7 +7497,7 @@
       <c r="G13">
         <v>11</v>
       </c>
-      <c r="L13" s="17"/>
+      <c r="L13" s="21"/>
       <c r="M13" s="8" t="s">
         <v>230</v>
       </c>
@@ -7516,7 +7516,7 @@
       <c r="R13" s="8">
         <v>150</v>
       </c>
-      <c r="S13" s="16" t="s">
+      <c r="S13" s="14" t="s">
         <v>227</v>
       </c>
       <c r="T13" s="9">
@@ -7527,7 +7527,7 @@
       <c r="G14">
         <v>12</v>
       </c>
-      <c r="L14" s="19"/>
+      <c r="L14" s="22"/>
       <c r="M14" s="9" t="s">
         <v>223</v>
       </c>
@@ -7557,7 +7557,7 @@
       <c r="G15">
         <v>13</v>
       </c>
-      <c r="L15" s="20" t="s">
+      <c r="L15" s="15" t="s">
         <v>227</v>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="16" t="s">
         <v>232</v>
       </c>
       <c r="L22" t="s">
@@ -7699,7 +7699,7 @@
       </c>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="17" t="s">
         <v>233</v>
       </c>
       <c r="L23" t="s">
@@ -7725,7 +7725,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="17" t="s">
         <v>234</v>
       </c>
       <c r="L24" t="s">
@@ -7754,7 +7754,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="17" t="s">
         <v>235</v>
       </c>
       <c r="L25" t="s">
@@ -7777,7 +7777,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="17" t="s">
         <v>236</v>
       </c>
       <c r="L26" t="s">
@@ -7803,7 +7803,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="17" t="s">
         <v>237</v>
       </c>
       <c r="L27" t="s">
@@ -7832,7 +7832,7 @@
       </c>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="17" t="s">
         <v>238</v>
       </c>
       <c r="L28" t="s">
@@ -7861,7 +7861,7 @@
       </c>
     </row>
     <row r="29" spans="1:19">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="17" t="s">
         <v>239</v>
       </c>
       <c r="L29" t="s">
